--- a/fix-errors/ig/FRSectionResultsLMCDAFHIR.xlsx
+++ b/fix-errors/ig/FRSectionResultsLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T08:13:43+00:00</t>
+    <t>2026-08-18T11:25:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -100,13 +100,13 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-observation-results</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-observation-results|0.1.0</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-resultats</t>
+    <t>https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-resultats|0.1.0</t>
   </si>
   <si>
     <t>FRLMObservationResults</t>
@@ -142,7 +142,7 @@
     <t>FRCDAResultats.entry:FRCDAResultats</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-composition-document</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-composition-document|0.1.0</t>
   </si>
   <si>
     <t>FRCompositionDocument.section:sectionResults</t>
